--- a/output/roomself_excel/8156.xlsx
+++ b/output/roomself_excel/8156.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>154584</v>
+        <v>122148</v>
       </c>
       <c r="D2" t="n">
-        <v>3624</v>
+        <v>2924</v>
       </c>
       <c r="E2" t="n">
-        <v>714</v>
+        <v>324</v>
       </c>
       <c r="F2" t="n">
-        <v>246</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>260482</v>
+        <v>83028</v>
       </c>
       <c r="D3" t="n">
-        <v>5036</v>
+        <v>2444</v>
       </c>
       <c r="E3" t="n">
-        <v>768</v>
+        <v>204</v>
       </c>
       <c r="F3" t="n">
-        <v>714</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>44807</v>
+        <v>38766</v>
       </c>
       <c r="D5" t="n">
-        <v>1728</v>
+        <v>1580</v>
       </c>
       <c r="E5" t="n">
-        <v>390</v>
+        <v>232</v>
       </c>
       <c r="F5" t="n">
-        <v>194</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38766</v>
+        <v>44807</v>
       </c>
       <c r="D6" t="n">
-        <v>1580</v>
+        <v>1728</v>
       </c>
       <c r="E6" t="n">
-        <v>232</v>
+        <v>173</v>
       </c>
       <c r="F6" t="n">
-        <v>201</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15960</v>
+        <v>55306</v>
       </c>
       <c r="D7" t="n">
-        <v>1096</v>
+        <v>2088</v>
       </c>
       <c r="E7" t="n">
-        <v>278</v>
+        <v>210</v>
       </c>
       <c r="F7" t="n">
-        <v>209</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -602,15 +602,59 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>154584</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3624</v>
+      </c>
+      <c r="E8" t="n">
+        <v>714</v>
+      </c>
+      <c r="F8" t="n">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>15960</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1096</v>
+      </c>
+      <c r="E9" t="n">
+        <v>84</v>
+      </c>
+      <c r="F9" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>21406</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D10" t="n">
         <v>1172</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E10" t="n">
         <v>202</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F10" t="n">
         <v>179</v>
       </c>
     </row>

--- a/output/roomself_excel/8156.xlsx
+++ b/output/roomself_excel/8156.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>2924</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>324</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>19</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +525,20 @@
       <c r="D3" t="n">
         <v>2444</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>204</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>19</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +555,20 @@
       <c r="D4" t="n">
         <v>2512</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>369</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>19</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,11 +585,27 @@
       <c r="D5" t="n">
         <v>1580</v>
       </c>
-      <c r="E5" t="n">
-        <v>232</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>201</v>
+        <v>213</v>
+      </c>
+      <c r="G5" t="n">
+        <v>19</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>182</v>
+      </c>
+      <c r="J5" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +623,20 @@
       <c r="D6" t="n">
         <v>1728</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>173</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>19</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +653,20 @@
       <c r="D7" t="n">
         <v>2088</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>210</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>19</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +683,27 @@
       <c r="D8" t="n">
         <v>3624</v>
       </c>
-      <c r="E8" t="n">
-        <v>714</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>246</v>
+        <v>678</v>
+      </c>
+      <c r="G8" t="n">
+        <v>18</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>456</v>
+      </c>
+      <c r="J8" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -629,12 +721,20 @@
       <c r="D9" t="n">
         <v>1096</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>84</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>19</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,11 +751,27 @@
       <c r="D10" t="n">
         <v>1172</v>
       </c>
-      <c r="E10" t="n">
-        <v>202</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>179</v>
+        <v>139</v>
+      </c>
+      <c r="G10" t="n">
+        <v>25</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>154</v>
+      </c>
+      <c r="J10" t="n">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
